--- a/analyze-words/report/history/keyword-table-20260709-155836.xlsx
+++ b/analyze-words/report/history/keyword-table-20260709-155836.xlsx
@@ -54,12 +54,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,9 +555,9 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -621,66 +632,80 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>image to text</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>image to text</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="3" t="n">
-        <v>621040</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L2" s="4" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>621040.0</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ocr online</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>ocr online</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="3" t="n">
-        <v>86640</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L3" s="4" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>86640.0</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L3"/>

--- a/analyze-words/report/history/keyword-table-20260709-155836.xlsx
+++ b/analyze-words/report/history/keyword-table-20260709-155836.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$3</definedName>
@@ -34,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -65,7 +75,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -436,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -500,17 +519,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>standardWordRows</t>
+          <t>simMatchedCount</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>scoredCount</t>
+          <t>simNoMatchCount</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -520,22 +539,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>scoreFormula</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>simWindowVolume * simCpc / simKd</t>
-        </is>
+          <t>simFailureCount</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>standardWordRows</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>scoredCount</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>scoreFormula</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>simWindowVolume * simCpc / simKd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>standardWordTableVersion</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
@@ -557,16 +606,16 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,52 +631,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>score(simWindowVolume*cpc/kd)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sim)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sim)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sim)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sem)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sem)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sem)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>gefeiKD</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sourcePresence(SIM/SEM)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>score(simWindowVolume*cpc/kd)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sim)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sim)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sim)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sem)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sem)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sem)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>gefeiKD</t>
         </is>
       </c>
     </row>
@@ -638,36 +687,30 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="n">
+        <v>621040</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>image to text</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>621040.0</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -676,36 +719,30 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="n">
+        <v>86640</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>ocr online</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>86640.0</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L3"/>
